--- a/03_Outputs/all/01_TablasDescriptivas/idx14_seguridad_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx14_seguridad_vr.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.193442750333163</v>
+        <v>1.193442750333161</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -419,7 +419,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9568529804815837</v>
+        <v>0.9568529804815835</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.593951306984597</v>
+        <v>0.5939513069845973</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3946420108052325</v>
+        <v>0.3946420108052324</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>3.054553701728592</v>
+        <v>3.054553701728591</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>23.86885500666323</v>
+        <v>23.86885500666321</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>19.13705960963166</v>
+        <v>19.13705960963165</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>11.87902613969193</v>
+        <v>11.87902613969194</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>7.892840216104643</v>
+        <v>7.89284021610464</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>61.09107403457179</v>
+        <v>61.09107403457177</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>80.22813364420344</v>
+        <v>80.22813364420342</v>
       </c>
       <c r="C19">
         <v>3</v>
